--- a/relax.xlsx
+++ b/relax.xlsx
@@ -125,6 +125,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>accuracy-check</author>
+  </authors>
+  <commentList>
+    <comment ref="M8" authorId="0" shapeId="0">
+      <text>
+        <t>Cr: agent input data/relax/Cr is Cr35 (35 atoms, E0=-329.38014). ground truth row is Cr2 (2 atoms, -19.009246). Totals NOT directly comparable; compare per-atom: agent -9.4109 vs GT -9.5046 eV/atom (Δ0.094).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1510,10 +1525,8 @@
       <c r="L8" t="n">
         <v>-152.38851</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
+      <c r="M8" t="n">
+        <v>-329.38014</v>
       </c>
       <c r="N8" t="n">
         <v>-96.208468</v>
@@ -1536,10 +1549,8 @@
       <c r="T8" t="n">
         <v>-683.00951</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
+      <c r="U8" t="n">
+        <v>-210.69189</v>
       </c>
       <c r="V8" t="n">
         <v>-193.24805</v>
@@ -1605,11 +1616,12 @@
         <v>-16.439068</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2948,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2978,6 +2990,11 @@
           <t>candidate_count</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3165,14 +3182,21 @@
           <t>Cr</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>-329.38014</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>runs/rx_Cr</t>
+        </is>
+      </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cr35 (35 atoms); GT is Cr2 (2 atoms) -&gt; compare per-atom (agent -9.4109 vs GT -9.5046 eV/atom). Converged (returncode 0).</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -3253,14 +3277,21 @@
           <t>Li10Ge(PS6)2</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>-210.69189</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>runs/rx_Li10Ge(PS6)2</t>
+        </is>
+      </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>49-atom cell, same as GT. Converged; matches GT (Δ0.076 eV).</t>
+        </is>
       </c>
     </row>
     <row r="18">
